--- a/SEM 6/Progress.xlsx
+++ b/SEM 6/Progress.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\degree\SEM 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2133E997-ADDE-42CE-B7CE-9BF2566E72D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A6D4565-4BB7-45D4-9FC5-EB3CC3C767F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -585,8 +585,8 @@
       <c r="D5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>30</v>
+      <c r="E5" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>29</v>
@@ -611,8 +611,8 @@
       <c r="F6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="6" t="s">
-        <v>30</v>
+      <c r="G6" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -622,8 +622,8 @@
       <c r="C7" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>30</v>
+      <c r="D7" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>30</v>

--- a/SEM 6/Progress.xlsx
+++ b/SEM 6/Progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\degree\SEM 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A6D4565-4BB7-45D4-9FC5-EB3CC3C767F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D9B313-BC7E-487B-BE52-77077B3287C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -579,8 +579,8 @@
       <c r="B5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>30</v>
+      <c r="C5" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>29</v>
@@ -642,8 +642,8 @@
       <c r="C8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>30</v>
+      <c r="D8" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>30</v>

--- a/SEM 6/Progress.xlsx
+++ b/SEM 6/Progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\degree\SEM 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D9B313-BC7E-487B-BE52-77077B3287C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5761655-DD35-4BED-9D00-12F67FB36816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -631,8 +631,8 @@
       <c r="F7" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>30</v>
+      <c r="G7" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">

--- a/SEM 6/Progress.xlsx
+++ b/SEM 6/Progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\degree\SEM 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5761655-DD35-4BED-9D00-12F67FB36816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB164BEA-D02E-4FC0-9575-A52E2B27B9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -599,8 +599,8 @@
       <c r="B6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>30</v>
+      <c r="C6" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>29</v>
@@ -651,8 +651,8 @@
       <c r="F8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>30</v>
+      <c r="G8" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">

--- a/SEM 6/Progress.xlsx
+++ b/SEM 6/Progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\degree\SEM 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB164BEA-D02E-4FC0-9575-A52E2B27B9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB99CC1-EFFD-423A-8E4E-0FC1C6DDE48C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -619,8 +619,8 @@
       <c r="B7" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>30</v>
+      <c r="C7" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>29</v>
@@ -628,8 +628,8 @@
       <c r="E7" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>30</v>
+      <c r="F7" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>29</v>
@@ -639,8 +639,8 @@
       <c r="B8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>30</v>
+      <c r="C8" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>29</v>
@@ -648,8 +648,8 @@
       <c r="E8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>30</v>
+      <c r="F8" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>29</v>
@@ -662,8 +662,8 @@
       <c r="C9" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>30</v>
+      <c r="D9" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>30</v>
@@ -771,8 +771,8 @@
       <c r="F14" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G14" s="6" t="s">
-        <v>30</v>
+      <c r="G14" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -782,8 +782,8 @@
       <c r="C15" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>30</v>
+      <c r="D15" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>30</v>
@@ -791,8 +791,8 @@
       <c r="F15" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G15" s="6" t="s">
-        <v>30</v>
+      <c r="G15" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -802,8 +802,8 @@
       <c r="C16" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>30</v>
+      <c r="D16" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>30</v>
@@ -811,8 +811,8 @@
       <c r="F16" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="6" t="s">
-        <v>30</v>
+      <c r="G16" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -822,8 +822,8 @@
       <c r="C17" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>30</v>
+      <c r="D17" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>30</v>
@@ -831,8 +831,8 @@
       <c r="F17" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G17" s="6" t="s">
-        <v>30</v>
+      <c r="G17" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -842,8 +842,8 @@
       <c r="C18" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>30</v>
+      <c r="D18" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>30</v>
@@ -851,8 +851,8 @@
       <c r="F18" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G18" s="6" t="s">
-        <v>30</v>
+      <c r="G18" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">

--- a/SEM 6/Progress.xlsx
+++ b/SEM 6/Progress.xlsx
@@ -8,17 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\degree\SEM 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB99CC1-EFFD-423A-8E4E-0FC1C6DDE48C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC1B1039-F2A0-45F5-BB22-D257DBDA24EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -671,8 +680,8 @@
       <c r="F9" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="6" t="s">
-        <v>30</v>
+      <c r="G9" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">

--- a/SEM 6/Progress.xlsx
+++ b/SEM 6/Progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\degree\SEM 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC1B1039-F2A0-45F5-BB22-D257DBDA24EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25B8B0FB-0EE5-449C-B6D3-57BD897870B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -668,8 +668,8 @@
       <c r="B9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>30</v>
+      <c r="C9" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>29</v>
@@ -677,8 +677,8 @@
       <c r="E9" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>30</v>
+      <c r="F9" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>29</v>
@@ -688,17 +688,17 @@
       <c r="B10" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>30</v>
+      <c r="C10" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>30</v>
+      <c r="F10" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>30</v>
@@ -768,17 +768,17 @@
       <c r="B14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>30</v>
+      <c r="C14" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>30</v>
+      <c r="E14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>15</v>
@@ -788,17 +788,17 @@
       <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>30</v>
+      <c r="C15" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>30</v>
+      <c r="E15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>15</v>
@@ -808,17 +808,17 @@
       <c r="B16" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>30</v>
+      <c r="C16" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>30</v>
+      <c r="E16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>15</v>
@@ -828,17 +828,17 @@
       <c r="B17" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>30</v>
+      <c r="C17" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>30</v>
+      <c r="E17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>15</v>
@@ -848,17 +848,17 @@
       <c r="B18" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>30</v>
+      <c r="C18" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>30</v>
+      <c r="E18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>15</v>

--- a/SEM 6/Progress.xlsx
+++ b/SEM 6/Progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\degree\SEM 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25B8B0FB-0EE5-449C-B6D3-57BD897870B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{169A7988-4BEB-4CF4-B620-EEB043F88F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -700,8 +700,8 @@
       <c r="F10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="6" t="s">
-        <v>30</v>
+      <c r="G10" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">

--- a/SEM 6/Progress.xlsx
+++ b/SEM 6/Progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\degree\SEM 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{169A7988-4BEB-4CF4-B620-EEB043F88F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE9D5360-1F07-436D-A1CD-924A9BE9A138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -882,8 +882,8 @@
       <c r="D20" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>15</v>
+      <c r="E20" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>15</v>

--- a/SEM 6/Progress.xlsx
+++ b/SEM 6/Progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\degree\SEM 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE9D5360-1F07-436D-A1CD-924A9BE9A138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B66D4032-5D89-492F-AB3F-838A436F2DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -708,11 +708,11 @@
       <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>30</v>
+      <c r="C11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>30</v>

--- a/SEM 6/Progress.xlsx
+++ b/SEM 6/Progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\degree\SEM 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B66D4032-5D89-492F-AB3F-838A436F2DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF4491BC-2F29-4A43-96D3-63EB2AF58121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="28">
   <si>
     <t>EXP1</t>
   </si>
@@ -87,24 +87,6 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>TUT1</t>
-  </si>
-  <si>
-    <t>TUT2</t>
-  </si>
-  <si>
-    <t>TUT3</t>
-  </si>
-  <si>
-    <t>TUT4</t>
-  </si>
-  <si>
-    <t>TUT5</t>
-  </si>
-  <si>
-    <t>TUT6</t>
-  </si>
-  <si>
     <t>EXP14</t>
   </si>
   <si>
@@ -130,6 +112,15 @@
   </si>
   <si>
     <t>Incomplete</t>
+  </si>
+  <si>
+    <t>ASS3</t>
+  </si>
+  <si>
+    <t>ASS4</t>
+  </si>
+  <si>
+    <t>ASS5</t>
   </si>
 </sst>
 </file>
@@ -539,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G28"/>
+  <dimension ref="B2:G25"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1"/>
@@ -549,19 +540,19 @@
   <sheetData>
     <row r="2" spans="2:7" ht="20.25" x14ac:dyDescent="0.25">
       <c r="C2" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -569,19 +560,19 @@
         <v>0</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -589,19 +580,19 @@
         <v>1</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -609,19 +600,19 @@
         <v>2</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -629,19 +620,19 @@
         <v>3</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -649,19 +640,19 @@
         <v>4</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -669,19 +660,19 @@
         <v>5</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -689,19 +680,19 @@
         <v>6</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -709,19 +700,19 @@
         <v>7</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -729,19 +720,19 @@
         <v>8</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -749,19 +740,19 @@
         <v>9</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -772,7 +763,7 @@
         <v>15</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>15</v>
@@ -826,7 +817,7 @@
     </row>
     <row r="17" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>15</v>
@@ -846,7 +837,7 @@
     </row>
     <row r="18" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>15</v>
@@ -877,47 +868,64 @@
         <v>13</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>15</v>
+      <c r="C21" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B22" s="3"/>
+      <c r="B22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="23" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B23" s="3" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>15</v>
@@ -931,13 +939,13 @@
       <c r="F23" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G23" s="4" t="s">
-        <v>15</v>
+      <c r="G23" s="6" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B24" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>15</v>
@@ -951,89 +959,12 @@
       <c r="F24" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G24" s="4" t="s">
-        <v>15</v>
+      <c r="G24" s="6" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B25" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B26" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B27" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B28" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>15</v>
-      </c>
+      <c r="B25" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/SEM 6/Progress.xlsx
+++ b/SEM 6/Progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\degree\SEM 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF4491BC-2F29-4A43-96D3-63EB2AF58121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E5083E-A225-4592-84BB-73B251253A6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -691,8 +691,8 @@
       <c r="F10" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>23</v>
+      <c r="G10" s="6" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -711,8 +711,8 @@
       <c r="F11" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="6" t="s">
-        <v>24</v>
+      <c r="G11" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -722,8 +722,8 @@
       <c r="C12" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>24</v>
+      <c r="D12" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>24</v>
@@ -731,8 +731,8 @@
       <c r="F12" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G12" s="6" t="s">
-        <v>24</v>
+      <c r="G12" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -742,8 +742,8 @@
       <c r="C13" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>24</v>
+      <c r="D13" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>24</v>
@@ -762,8 +762,8 @@
       <c r="C14" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>24</v>
+      <c r="D14" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>15</v>

--- a/SEM 6/Progress.xlsx
+++ b/SEM 6/Progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\degree\SEM 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E5083E-A225-4592-84BB-73B251253A6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC5E823C-AF46-4D92-94D5-9255A69C56E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="25">
   <si>
     <t>EXP1</t>
   </si>
@@ -112,15 +112,6 @@
   </si>
   <si>
     <t>Incomplete</t>
-  </si>
-  <si>
-    <t>ASS3</t>
-  </si>
-  <si>
-    <t>ASS4</t>
-  </si>
-  <si>
-    <t>ASS5</t>
   </si>
 </sst>
 </file>
@@ -530,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G25"/>
+  <dimension ref="B2:G22"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1"/>
@@ -719,8 +710,8 @@
       <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>24</v>
+      <c r="C12" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>23</v>
@@ -739,8 +730,8 @@
       <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>24</v>
+      <c r="C13" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>23</v>
@@ -904,67 +895,7 @@
       </c>
     </row>
     <row r="22" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B23" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B24" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B25" s="3"/>
+      <c r="B22" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/SEM 6/Progress.xlsx
+++ b/SEM 6/Progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\degree\SEM 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC5E823C-AF46-4D92-94D5-9255A69C56E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0043F277-45DE-4EFC-AF10-EA8206812CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -867,8 +867,8 @@
       <c r="E20" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F20" s="6" t="s">
-        <v>24</v>
+      <c r="F20" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>24</v>
@@ -878,8 +878,8 @@
       <c r="B21" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>24</v>
+      <c r="C21" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>24</v>
@@ -887,8 +887,8 @@
       <c r="E21" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F21" s="6" t="s">
-        <v>24</v>
+      <c r="F21" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>24</v>

--- a/SEM 6/Progress.xlsx
+++ b/SEM 6/Progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\degree\SEM 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0043F277-45DE-4EFC-AF10-EA8206812CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{310379CC-BAEC-477E-A64B-C7B5CB15E327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -870,8 +870,8 @@
       <c r="F20" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G20" s="6" t="s">
-        <v>24</v>
+      <c r="G20" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -890,8 +890,8 @@
       <c r="F21" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G21" s="6" t="s">
-        <v>24</v>
+      <c r="G21" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">

--- a/SEM 6/Progress.xlsx
+++ b/SEM 6/Progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\degree\SEM 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{310379CC-BAEC-477E-A64B-C7B5CB15E327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{932CB65E-E125-4EBB-AD1F-9FFEEDBBE782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -682,8 +682,8 @@
       <c r="F10" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="6" t="s">
-        <v>24</v>
+      <c r="G10" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -742,8 +742,8 @@
       <c r="F13" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>24</v>
+      <c r="G13" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -861,8 +861,8 @@
       <c r="C20" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>24</v>
+      <c r="D20" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>23</v>
@@ -881,8 +881,8 @@
       <c r="C21" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>24</v>
+      <c r="D21" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>24</v>

--- a/SEM 6/Progress.xlsx
+++ b/SEM 6/Progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\degree\SEM 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{932CB65E-E125-4EBB-AD1F-9FFEEDBBE782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFAA4871-CF5F-404B-80B8-9E6612A9031B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="21">
   <si>
     <t>EXP1</t>
   </si>
@@ -69,15 +69,6 @@
     <t>EXP10</t>
   </si>
   <si>
-    <t>EXP11</t>
-  </si>
-  <si>
-    <t>EXP12</t>
-  </si>
-  <si>
-    <t>EXP13</t>
-  </si>
-  <si>
     <t>ASS1</t>
   </si>
   <si>
@@ -87,12 +78,6 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>EXP14</t>
-  </si>
-  <si>
-    <t>EXP15</t>
-  </si>
-  <si>
     <t>DS</t>
   </si>
   <si>
@@ -112,6 +97,9 @@
   </si>
   <si>
     <t>Incomplete</t>
+  </si>
+  <si>
+    <t>Mini Project</t>
   </si>
 </sst>
 </file>
@@ -521,7 +509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G22"/>
+  <dimension ref="B2:G18"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1"/>
@@ -531,19 +519,19 @@
   <sheetData>
     <row r="2" spans="2:7" ht="20.25" x14ac:dyDescent="0.25">
       <c r="C2" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -551,19 +539,19 @@
         <v>0</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -571,19 +559,19 @@
         <v>1</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -591,19 +579,19 @@
         <v>2</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -611,19 +599,19 @@
         <v>3</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>24</v>
+        <v>18</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -631,19 +619,19 @@
         <v>4</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>24</v>
+        <v>18</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -651,19 +639,19 @@
         <v>5</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>24</v>
+        <v>18</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -671,19 +659,19 @@
         <v>6</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>24</v>
+        <v>18</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -691,19 +679,19 @@
         <v>7</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>24</v>
+        <v>18</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -711,19 +699,19 @@
         <v>8</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>24</v>
+        <v>18</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -731,171 +719,91 @@
         <v>9</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>24</v>
+        <v>18</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>15</v>
-      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
     </row>
     <row r="15" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="3"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B17" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B18" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="G18" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-    </row>
-    <row r="20" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B20" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B21" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B22" s="3"/>
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/SEM 6/Progress.xlsx
+++ b/SEM 6/Progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\degree\SEM 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFAA4871-CF5F-404B-80B8-9E6612A9031B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F52EE7D-53F7-4C9C-BDEF-AC38CCD091F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -584,8 +584,8 @@
       <c r="D6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>19</v>
+      <c r="E6" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>18</v>

--- a/SEM 6/Progress.xlsx
+++ b/SEM 6/Progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\degree\SEM 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F52EE7D-53F7-4C9C-BDEF-AC38CCD091F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B066C9EC-65F7-4A59-AFD7-F38FAFCD2B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="20">
   <si>
     <t>EXP1</t>
   </si>
@@ -94,9 +94,6 @@
   </si>
   <si>
     <t>Completed</t>
-  </si>
-  <si>
-    <t>Incomplete</t>
   </si>
   <si>
     <t>Mini Project</t>
@@ -106,7 +103,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -154,25 +151,12 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Microsoft JhengHei UI Light"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Microsoft JhengHei UI Light"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -189,11 +173,6 @@
         <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -204,13 +183,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -220,16 +198,12 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="3">
     <cellStyle name="Accent3" xfId="1" builtinId="37"/>
-    <cellStyle name="Bad" xfId="3" builtinId="27"/>
     <cellStyle name="Good" xfId="2" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -787,7 +761,7 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>18</v>
@@ -795,8 +769,8 @@
       <c r="D18" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>19</v>
+      <c r="E18" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>12</v>
